--- a/data/trans_bre/P1408-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1408-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,54</t>
+          <t>2,28</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; -0,26</t>
+          <t>-2,25; -0,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -670,17 +670,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,0</t>
+          <t>-1,47; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 7,36</t>
+          <t>0,61; 6,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 133,84</t>
+          <t>-100,0; 250,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>121,29%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 2,3</t>
+          <t>-0,49; 2,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,55</t>
+          <t>-0,3; 0,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,02</t>
+          <t>-0,51; 1,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,99</t>
+          <t>-0,54; 1,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,7; 399,29</t>
+          <t>-37,08; 363,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,66</t>
+          <t>-0,71; 1,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,79</t>
+          <t>-1,01; 0,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,85</t>
+          <t>-0,67; 0,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,91</t>
+          <t>-0,81; 0,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-52,18; 307,67</t>
+          <t>-49,38; 298,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-79,31; 303,62</t>
+          <t>-86,11; 293,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>-14,32%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,31</t>
+          <t>-2,18; 2,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,89</t>
+          <t>-1,95; 0,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,44</t>
+          <t>-1,61; 0,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,52</t>
+          <t>-1,95; 0,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,78; 142,49</t>
+          <t>-52,28; 117,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-91,55; 329,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-89,16; 123,06</t>
+          <t>-90,53; 130,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-57,01; 225,92</t>
+          <t>-60,88; 77,44</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-9,44%</t>
+          <t>-11,52%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,11; -1,2</t>
+          <t>-6,99; -1,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 0,63</t>
+          <t>-4,17; 0,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,64; -0,73</t>
+          <t>-5,39; -0,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,42</t>
+          <t>-2,03; 1,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-84,57; -20,81</t>
+          <t>-85,68; -24,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-80,02; 39,63</t>
+          <t>-77,43; 50,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-88,66; -10,37</t>
+          <t>-89,51; -18,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-50,5; 66,35</t>
+          <t>-48,49; 59,56</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,83</t>
+          <t>-2,08</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-58,58%</t>
+          <t>-32,99%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,71; -0,59</t>
+          <t>-9,73; -1,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,58; -1,52</t>
+          <t>-7,47; -1,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 2,48</t>
+          <t>-3,52; 2,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,4; -1,39</t>
+          <t>-4,51; 0,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-68,31; -4,89</t>
+          <t>-70,03; -9,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-90,87; -28,99</t>
+          <t>-90,59; -26,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-63,08; 111,76</t>
+          <t>-62,01; 85,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-87,47; -25,1</t>
+          <t>-58,98; 7,28</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,08</t>
+          <t>-1,79</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-24,17%</t>
+          <t>-21,66%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-21,06; -8,0</t>
+          <t>-19,99; -8,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,92; -2,78</t>
+          <t>-11,7; -2,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,68; -0,22</t>
+          <t>-6,99; 0,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 0,74</t>
+          <t>-4,8; 1,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-79,79; -44,98</t>
+          <t>-78,8; -45,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-79,86; -30,1</t>
+          <t>-79,79; -31,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-73,96; 9,11</t>
+          <t>-73,86; 21,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-47,55; 11,1</t>
+          <t>-47,77; 18,2</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,31; -0,53</t>
+          <t>-2,3; -0,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,65; -0,37</t>
+          <t>-1,59; -0,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,24; -0,05</t>
+          <t>-1,29; -0,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,76</t>
+          <t>-0,67; 0,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,09; -14,79</t>
+          <t>-50,59; -16,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,11; -18,5</t>
+          <t>-62,96; -15,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-55,12; -2,5</t>
+          <t>-57,23; -1,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 37,78</t>
+          <t>-23,1; 32,4</t>
         </is>
       </c>
     </row>
